--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0064.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0064.xlsx
@@ -5319,7 +5319,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Samousas à? Cậu làm gì ở đây thế? Ta vừa nghe thấy cậu hét lên "bộ bài" với "bậc thầy đối决 tối thượng" à? Chuyện gì đang xảy ra vậy?</t>
+          <t>Samousas à? Cậu làm gì ở đây thế? Ta vừa nghe thấy cậu hét lên "bộ bài" với "bậc thầy đối quyết tối thượng" à? Chuyện gì đang xảy ra vậy?</t>
         </is>
       </c>
     </row>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Bạn đang làm gì ở đây?</t>
+          <t>Cậu làm gì ở đây vậy?</t>
         </is>
       </c>
     </row>
@@ -8179,7 +8179,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Nhưng ta... ừ, ta cũng sẽ cố hết sức.</t>
+          <t>Nhưng tao... ừ, tao cũng sẽ cố hết sức.</t>
         </is>
       </c>
     </row>
@@ -8309,7 +8309,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Sau đó, ta sẽ đưa cậu đến trái tim đang đập của Septimont, &lt;color=Highlight&gt;Capitoline Hill&lt;/color&gt;.</t>
+          <t>Sau đó, ta sẽ đưa cậu đến trái tim đang đập của Septimont, &lt;color=Highlight&gt;Đồi Capitoline&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Được rồi! Màu xanh tươi đẹp của &lt;color=Highlight&gt;Capitoline Hill&lt;/color&gt; đang đợi chúng ta!</t>
+          <t>Được rồi! Màu xanh tươi đẹp của &lt;color=Highlight&gt;Đồi Capitoline&lt;/color&gt; đang đợi chúng ta!</t>
         </is>
       </c>
     </row>
@@ -10649,7 +10649,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Ta biết ngươi đã bám đuôi bọn ta suốt từ nãy đến giờ.</t>
+          <t>Tao biết mày đã bám đuôi bọn tao suốt từ nãy đến giờ.</t>
         </is>
       </c>
     </row>
@@ -11624,7 +11624,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Bọn cậu cãi nhau chuyện gì vậy?</t>
+          <t>Bọn mày cãi nhau chuyện gì vậy?</t>
         </is>
       </c>
     </row>
@@ -14679,7 +14679,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Để đến được &lt;color=Highlight&gt;Statue of Fabius the Hero&lt;/color&gt;, chúng ta phải vượt qua biển này trước. Đường đi không ngắn đâu, vậy nên hãy lên đường ngay thôi!</t>
+          <t>Để đến được &lt;color=Highlight&gt;Tượng đài Anh hùng Fabius&lt;/color&gt;, chúng ta phải vượt qua biển này trước. Đường đi không ngắn đâu, vậy nên hãy lên đường ngay thôi!</t>
         </is>
       </c>
     </row>
@@ -15069,7 +15069,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Để ta giới thiệu lại về bản thân. Ta là Postumia, sử gia chính thức tương lai của Septimont!</t>
+          <t>Để tao giới thiệu lại về bản thân. Ta là Postumia, sử gia chính thức tương lai của Septimont!</t>
         </is>
       </c>
     </row>
@@ -15394,7 +15394,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Nghe này, hồi đầu ta tưởng chỉ cần làm theo đúng quy trình tập luyện, rồi cuối cùng nói thẳng là ta không thích kế hoạch của hắn thôi.</t>
+          <t>Nghe này, hồi đầu tao tưởng chỉ cần làm theo đúng quy trình tập luyện, rồi cuối cùng nói thẳng là tao không thích kế hoạch của hắn thôi.</t>
         </is>
       </c>
     </row>
@@ -16174,7 +16174,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Điểm đến tiếp theo, &lt;color=Highlight&gt;Border Mountains&lt;/color&gt;!</t>
+          <t>Điểm đến tiếp theo, &lt;color=Highlight&gt;Núi Biên Giới&lt;/color&gt;!</t>
         </is>
       </c>
     </row>
@@ -24104,7 +24104,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Cậu! Cậu chính là người chơi hoàn hảo cho Peaks of Prestige!</t>
+          <t>Mày! Mày chính là người chơi hoàn hảo cho Peaks of Prestige!</t>
         </is>
       </c>
     </row>
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Đỉnh Vinh Quang? Cái tên gì vậy? Ta không chơi đâu.</t>
+          <t>Đỉnh Vinh Quang? Cái tên gì vậy? Tao không chơi đâu.</t>
         </is>
       </c>
     </row>
@@ -25079,7 +25079,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Có phần thưởng không?</t>
+          <t>Có phần thưởng chứ?</t>
         </is>
       </c>
     </row>
@@ -25924,7 +25924,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Hãy tham gia Đỉnh Cao Danh Vọng! Vô số tiếng vọng. Chiến thuật vô biên. Người tiếp theo có thể là Bậc Thầy Đấu Đỉnh!&lt;/b&gt;</t>
+          <t>&lt;b&gt;Hãy tham gia Đỉnh Cao Danh Vọng! Vô số Echo. Chiến thuật vô biên. Người tiếp theo có thể là Bậc Thầy Đấu Đỉnh!&lt;/b&gt;</t>
         </is>
       </c>
     </row>
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Chuyện gì đang xảy ra vậy?</t>
+          <t>Có chuyện gì vậy?</t>
         </is>
       </c>
     </row>
@@ -27159,7 +27159,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Sao tự dưng ta lại có cảm giác mình mới là kẻ thách đấu vậy...</t>
+          <t>Sao tự dưng tao lại có cảm giác mình mới là kẻ thách đấu vậy...</t>
         </is>
       </c>
     </row>
@@ -27354,7 +27354,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Thôi, không từ chối được rồi. Để ta thử một miếng trước đã. Nếu ngon thì...</t>
+          <t>Thôi, không từ chối được rồi. Để tao thử một miếng trước đã. Nếu ngon thì...</t>
         </is>
       </c>
     </row>
@@ -28394,7 +28394,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Và cái gì? Ta đánh bại hết tụi nó chứ còn gì! Hahaha! Khá ấn tượng phải không, bạn thân?</t>
+          <t>Và cái gì? Tao đánh bại hết tụi nó chứ còn gì! Hahaha! Khá ấn tượng phải không, bạn thân?</t>
         </is>
       </c>
     </row>
@@ -30344,7 +30344,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Và cái gì? Ta đánh bại hết tụi nó chứ còn gì! Hahaha! Khá ấn tượng phải không, bạn thân?</t>
+          <t>Và cái gì? Tao đánh bại hết tụi nó chứ còn gì! Hahaha! Khá ấn tượng phải không, bạn thân?</t>
         </is>
       </c>
     </row>
@@ -31774,7 +31774,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Haha! Ta cá là tiếng tăm cuộc đấu kinh thiên động địa của chúng ta sẽ vang khắp Septimont!</t>
+          <t>Haha! Tao cá là tiếng tăm cuộc đấu kinh thiên động địa của chúng ta sẽ vang khắp Septimont!</t>
         </is>
       </c>
     </row>
@@ -31904,7 +31904,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Ta là người may mắn vô biên đấy, bạn ơi! Chỉ hơi thiếu chiến thuật tí thôi...</t>
+          <t>Tao là người may mắn vô biên đấy, bạn ơi! Chỉ hơi thiếu chiến thuật tí thôi...</t>
         </is>
       </c>
     </row>
@@ -32359,7 +32359,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Có việc gì mà cậu lại đến Septimont vậy?</t>
+          <t>Có việc gì mà bạn lại đến Septimont vậy?</t>
         </is>
       </c>
     </row>
@@ -32684,7 +32684,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Haha, ta thích nghĩ chúng ta như những hiệp sĩ trong truyện hơn.</t>
+          <t>Haha, tao thích nghĩ chúng ta như những hiệp sĩ trong truyện hơn.</t>
         </is>
       </c>
     </row>
@@ -33009,7 +33009,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Rồi ta nghe nói về cuộc thi đấu võ đài ở Septimont. Một sân khấu nơi vô số câu chuyện sẽ được khai sinh! Sao ta có thể bỏ lỡ chứ?</t>
+          <t>Rồi tao nghe nói về cuộc thi đấu võ đài ở Septimont. Một sân khấu nơi vô số câu chuyện sẽ được khai sinh! Sao tao có thể bỏ lỡ chứ?</t>
         </is>
       </c>
     </row>
